--- a/03_Outputs/Penderisco_Sinifana/09_Salud/salud.xlsx
+++ b/03_Outputs/Penderisco_Sinifana/09_Salud/salud.xlsx
@@ -1061,7 +1061,7 @@
         <v>4.17562578104116</v>
       </c>
       <c r="F10" s="9">
-        <v>255.626777679986</v>
+        <v>255.626777679987</v>
       </c>
       <c r="G10" s="11">
         <v>23.2165407890586</v>
